--- a/literature-review/snowballing/snowballing_topic2.xlsx
+++ b/literature-review/snowballing/snowballing_topic2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33836A4-1CA5-48D1-9D6A-4C7C3D34D9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EBEBCE-A473-4829-9F90-9A1011458A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13080" yWindow="1620" windowWidth="26556" windowHeight="14472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8304" yWindow="2208" windowWidth="30960" windowHeight="14244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>Backward Snowballing Results</t>
   </si>
@@ -90,56 +90,29 @@
     <t>Forward Snowballing Results</t>
   </si>
   <si>
-    <t>Enhancing Voice Authentication with a Hybrid Deep Learning and Active Learning Approach for Deepfake Detection</t>
-  </si>
-  <si>
-    <t>AS Ahmed, AM Khaleel</t>
-  </si>
-  <si>
     <t>ARTICLE</t>
   </si>
   <si>
-    <t>Journal of Robotics and Control (JRC)</t>
-  </si>
-  <si>
-    <t>https://journal.umy.ac.id/index.php/jrc/article/download/23502/9600</t>
-  </si>
-  <si>
     <t>✅</t>
   </si>
   <si>
-    <t>A taxonomy of multi-layered runtime guardrails for designing foundation model-based agents: Swiss cheese model for ai safety by design</t>
-  </si>
-  <si>
-    <t>M Shamsujjoha, Q Lu, D Zhao, L Zhu</t>
-  </si>
-  <si>
-    <t>arXiv preprint</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2408.02205</t>
-  </si>
-  <si>
-    <t>Deep active learning for computer vision: Past and future</t>
-  </si>
-  <si>
-    <t>R Takezoe, X Liu, S Mao, MT Chen</t>
-  </si>
-  <si>
-    <t>APSIPA Transactions on Signal and Information Processing</t>
-  </si>
-  <si>
-    <t>https://www.nowpublishers.com/article/OpenAccessDownload/SIP-2022-0057</t>
-  </si>
-  <si>
-    <t>Note: For this topic,multiple grey literature sources and tools were identified. They are listed separately in grey_literature.xslx</t>
+    <t>Saturn Platform: Foundation Model Operations and Generative AI for Financial Services</t>
+  </si>
+  <si>
+    <t>Busson, A.J., Gaio, R., Rocha, R.H., Evangelista, F., Rizzi, B., Carvalho, L., Miceli, R., Rabaioli, M. and Favaro, D.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2312.07721</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +144,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -181,12 +162,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFC4D79B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -234,20 +215,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -259,28 +232,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC4D79B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -555,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -565,12 +540,12 @@
     <col min="9" max="16" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="I2" s="2" t="s">
         <v>1</v>
       </c>
@@ -581,7 +556,7 @@
       </c>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -609,7 +584,7 @@
       <c r="I3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="4" t="s">
@@ -635,211 +610,135 @@
       </c>
       <c r="R3" s="7"/>
     </row>
-    <row r="4" spans="1:34" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:18" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>0</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="9">
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="11">
         <v>2023</v>
       </c>
-      <c r="E4" s="9">
-        <v>19</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="15" t="s">
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="S4"/>
-      <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
-      <c r="AE4"/>
-      <c r="AF4"/>
-      <c r="AG4"/>
-      <c r="AH4"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:34" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="I9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R10" s="7"/>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
-        <v>0</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="I10" s="14"/>
+      <c r="J10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="9">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
-        <v>1</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2024</v>
-      </c>
-      <c r="E12" s="9">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>35</v>
-      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="9"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H16" s="8"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H17" s="8"/>
@@ -847,16 +746,11 @@
     <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H21" s="8"/>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H10" r:id="rId1" xr:uid="{0F3630A9-D29E-4AB7-BD6D-11AA22466C5C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>